--- a/Improve_Eng/learning_log.xlsx
+++ b/Improve_Eng/learning_log.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -768,6 +768,123 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>수동태</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Passive Voice</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>오늘 문법 규칙을 퀴즈 문제 해설에서 확인하세요.</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>I have worked here for five years.</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>① '어제' 같은 과거 시점과 현재완료 혼용 ② have+동사원형 실수</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>Merriam-Webster Word of the Day</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>august</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>Today we're looking at a common English expression used in business settings. When someone says 'Let's take this offline,' they mean continuing a conversation privately, outside the current meeting.</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>offline — 회의 밖에서 (오프라인 X); take [something] offline — 나중에 따로 논의하다</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>Let's circle back</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>나중에 다시 돌아오다</t>
+        </is>
+      </c>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t>Let's circle back on the budget after the Q2 data arrives.</t>
+        </is>
+      </c>
+      <c r="O3" s="9" t="inlineStr">
+        <is>
+          <t>어말 자음 탈락 방지</t>
+        </is>
+      </c>
+      <c r="P3" s="9" t="inlineStr">
+        <is>
+          <t>한국어는 받침 뒤 모음을 붙이는 경향 — 마지막 자음만 닫고 끝내기</t>
+        </is>
+      </c>
+      <c r="Q3" s="9" t="inlineStr">
+        <is>
+          <t>fact /fækt/ | next /nekst/ | helped /helpt/ | asked /æskt/</t>
+        </is>
+      </c>
+      <c r="R3" s="9" t="inlineStr">
+        <is>
+          <t>allocate — 할당하다, 배정하다  |  allocate resources / allocate time / allocate budget</t>
+        </is>
+      </c>
+      <c r="S3" s="9" t="inlineStr"/>
+      <c r="T3" s="9" t="inlineStr"/>
+      <c r="U3" s="9" t="inlineStr">
+        <is>
+          <t>Topic Sentence 스캔</t>
+        </is>
+      </c>
+      <c r="V3" s="9" t="inlineStr">
+        <is>
+          <t>The global economy has shown signs of recovery. Consumer spending increased by 3% last quarter. However, inflation remains a concern for policymakers.</t>
+        </is>
+      </c>
+      <c r="W3" s="9" t="inlineStr">
+        <is>
+          <t>mentor</t>
+        </is>
+      </c>
+      <c r="X3" s="9" t="inlineStr">
+        <is>
+          <t>멘토, 스승</t>
+        </is>
+      </c>
+      <c r="Y3" s="9" t="inlineStr">
+        <is>
+          <t>오디세우스가 트로이 전쟁 중 아들 텔레마코스 교육을 맡긴 현자의 이름에서</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
